--- a/data/trans_orig/Q24A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fuman al día</t>
+          <t>Número medio de cigarrillos que fuman al día (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 13,61</t>
+          <t>11,52; 13,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,84</t>
+          <t>11,11; 13,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 13,08</t>
+          <t>10,1; 12,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,95</t>
+          <t>5,55; 10,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 11,24</t>
+          <t>9,27; 11,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,57</t>
+          <t>9,28; 11,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,1</t>
+          <t>7,61; 9,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,14</t>
+          <t>6,57; 10,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,09</t>
+          <t>10,81; 12,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,3</t>
+          <t>10,44; 12,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 11,16</t>
+          <t>9,36; 11,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,33</t>
+          <t>6,23; 9,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 16,11</t>
+          <t>14,73; 16,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 14,49</t>
+          <t>12,9; 14,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,32</t>
+          <t>12,21; 14,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 14,91</t>
+          <t>11,53; 14,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,94; 13,19</t>
+          <t>10,94; 13,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 12,35</t>
+          <t>10,58; 12,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,56</t>
+          <t>8,77; 10,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,65</t>
+          <t>7,58; 9,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,81</t>
+          <t>13,5; 14,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 13,29</t>
+          <t>12,12; 13,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 12,3</t>
+          <t>10,86; 12,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,2</t>
+          <t>10,11; 12,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 19,66</t>
+          <t>17,47; 19,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,54; 19,0</t>
+          <t>16,52; 18,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,43; 15,57</t>
+          <t>13,51; 15,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,95</t>
+          <t>12,42; 16,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,33</t>
+          <t>12,4; 14,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 14,58</t>
+          <t>12,5; 14,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 12,32</t>
+          <t>10,54; 12,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,1</t>
+          <t>8,39; 10,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 17,09</t>
+          <t>15,54; 17,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 16,66</t>
+          <t>15,04; 16,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 13,89</t>
+          <t>12,39; 13,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,78</t>
+          <t>10,82; 12,91</t>
         </is>
       </c>
     </row>
@@ -1136,57 +1136,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 21,18</t>
+          <t>18,45; 20,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 19,38</t>
+          <t>17,08; 19,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 16,6</t>
+          <t>14,63; 16,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 16,04</t>
+          <t>13,91; 15,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 16,45</t>
+          <t>13,33; 16,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,59</t>
+          <t>12,52; 14,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 14,01</t>
+          <t>11,88; 14,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 11,14</t>
+          <t>9,64; 11,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 18,93</t>
+          <t>16,84; 18,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 16,9</t>
+          <t>15,33; 16,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 15,13</t>
+          <t>13,57; 15,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 21,41</t>
+          <t>17,09; 21,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,46; 20,07</t>
+          <t>16,62; 20,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 17,46</t>
+          <t>13,98; 17,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,85</t>
+          <t>13,33; 15,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 16,14</t>
+          <t>11,05; 16,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 18,09</t>
+          <t>12,57; 18,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 13,04</t>
+          <t>10,19; 13,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,2</t>
+          <t>9,27; 11,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 19,41</t>
+          <t>15,94; 19,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 18,73</t>
+          <t>15,84; 18,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 15,01</t>
+          <t>12,59; 15,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 13,6</t>
+          <t>12,02; 13,71</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,12; 18,71</t>
+          <t>14,02; 18,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,9; 21,54</t>
+          <t>12,74; 21,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,4</t>
+          <t>11,1; 15,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 19,83</t>
+          <t>14,33; 19,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 26,36</t>
+          <t>9,35; 26,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,87</t>
+          <t>9,66; 18,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,16</t>
+          <t>7,49; 12,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 12,16</t>
+          <t>9,51; 12,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,86</t>
+          <t>14,34; 18,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,49; 19,15</t>
+          <t>12,98; 19,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,61</t>
+          <t>10,34; 13,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 15,96</t>
+          <t>12,57; 16,09</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 19,06</t>
+          <t>9,52; 19,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 20,04</t>
+          <t>10,2; 21,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 16,28</t>
+          <t>9,15; 15,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,93</t>
+          <t>9,12; 14,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 10,47</t>
+          <t>2,98; 10,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,22</t>
+          <t>6,56; 15,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,57</t>
+          <t>10,05; 18,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 18,94</t>
+          <t>8,22; 17,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,27</t>
+          <t>7,61; 13,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,06</t>
+          <t>9,45; 13,98</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,36</t>
+          <t>16,3; 17,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,67</t>
+          <t>15,56; 16,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,64</t>
+          <t>13,61; 14,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,96; 14,33</t>
+          <t>12,89; 14,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,19</t>
+          <t>12,1; 13,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,16</t>
+          <t>12,06; 13,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,44</t>
+          <t>10,49; 11,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,01</t>
+          <t>9,11; 10,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,87; 15,66</t>
+          <t>14,82; 15,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,22; 15,01</t>
+          <t>14,24; 15,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,35; 13,11</t>
+          <t>12,37; 13,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,29</t>
+          <t>11,37; 12,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,41</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>8,17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>7,82</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 13,5</t>
+          <t>11,39; 13,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 13,94</t>
+          <t>11,06; 13,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,96</t>
+          <t>10,1; 12,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,05</t>
+          <t>5,68; 9,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 11,19</t>
+          <t>9,32; 11,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 11,48</t>
+          <t>9,16; 11,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,9</t>
+          <t>7,5; 9,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,51</t>
+          <t>6,54; 10,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 12,16</t>
+          <t>10,76; 12,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 12,18</t>
+          <t>10,47; 12,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 11,22</t>
+          <t>9,23; 11,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,38</t>
+          <t>6,52; 9,43</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>11,24</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,73; 16,19</t>
+          <t>14,67; 16,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 14,54</t>
+          <t>12,87; 14,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 14,3</t>
+          <t>12,25; 14,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 14,8</t>
+          <t>11,7; 14,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,94; 13,21</t>
+          <t>10,83; 13,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 12,34</t>
+          <t>10,57; 12,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 10,54</t>
+          <t>8,75; 10,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 9,69</t>
+          <t>7,6; 9,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 14,71</t>
+          <t>13,48; 14,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 13,36</t>
+          <t>12,15; 13,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 12,29</t>
+          <t>10,84; 12,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,16</t>
+          <t>10,19; 12,33</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,9</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,23</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>11,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 19,64</t>
+          <t>17,37; 19,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 18,94</t>
+          <t>16,32; 18,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 15,51</t>
+          <t>13,4; 15,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,13</t>
+          <t>12,4; 15,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 14,37</t>
+          <t>12,36; 14,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 14,56</t>
+          <t>12,56; 14,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,43</t>
+          <t>10,54; 12,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 10,11</t>
+          <t>8,5; 10,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,54; 17,12</t>
+          <t>15,37; 17,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,04; 16,71</t>
+          <t>15,04; 16,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 13,87</t>
+          <t>12,48; 13,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 12,91</t>
+          <t>10,87; 12,79</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,97</t>
+          <t>15,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>10,41</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 20,98</t>
+          <t>18,46; 20,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 19,28</t>
+          <t>17,12; 19,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 16,73</t>
+          <t>14,53; 16,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,91; 15,99</t>
+          <t>14,25; 16,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 16,35</t>
+          <t>13,39; 16,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 14,62</t>
+          <t>12,64; 14,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,02</t>
+          <t>11,9; 14,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 11,11</t>
+          <t>9,64; 11,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 18,92</t>
+          <t>16,89; 18,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 16,96</t>
+          <t>15,3; 16,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 15,09</t>
+          <t>13,69; 15,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,51</t>
+          <t>12,27; 13,8</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>12,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 21,58</t>
+          <t>16,96; 21,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 20,3</t>
+          <t>16,44; 20,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 17,35</t>
+          <t>14,05; 17,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,33; 15,87</t>
+          <t>13,27; 15,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,08</t>
+          <t>11,08; 15,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,19</t>
+          <t>12,53; 17,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 13,08</t>
+          <t>10,24; 13,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 11,08</t>
+          <t>9,32; 11,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,94; 19,53</t>
+          <t>15,8; 19,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,84; 18,87</t>
+          <t>15,66; 18,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 15,06</t>
+          <t>12,72; 15,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,71</t>
+          <t>11,92; 13,45</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>10,41</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>14,0</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 18,66</t>
+          <t>13,9; 18,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 21,7</t>
+          <t>12,86; 21,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,32</t>
+          <t>11,0; 15,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 19,95</t>
+          <t>14,33; 19,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 26,36</t>
+          <t>9,92; 26,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,97</t>
+          <t>9,73; 18,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,2</t>
+          <t>7,61; 12,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,31</t>
+          <t>9,07; 11,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,92</t>
+          <t>14,4; 18,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 19,29</t>
+          <t>12,81; 19,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 13,71</t>
+          <t>10,41; 13,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 16,09</t>
+          <t>12,52; 16,33</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>10,61</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,52; 19,91</t>
+          <t>9,77; 19,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 21,09</t>
+          <t>9,94; 20,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,78</t>
+          <t>9,05; 15,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,89</t>
+          <t>9,42; 15,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,0</t>
+          <t>2,0; 3,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,03</t>
+          <t>3,0; 10,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 15,26</t>
+          <t>5,79; 14,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 18,55</t>
+          <t>10,0; 18,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 17,86</t>
+          <t>8,16; 17,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,75</t>
+          <t>7,51; 13,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,45; 13,98</t>
+          <t>9,48; 13,96</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>11,93</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,36</t>
+          <t>16,36; 17,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,69</t>
+          <t>15,56; 16,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,61; 14,66</t>
+          <t>13,63; 14,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 14,31</t>
+          <t>13,09; 14,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,1; 13,22</t>
+          <t>12,08; 13,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,1</t>
+          <t>12,04; 13,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,49; 11,44</t>
+          <t>10,53; 11,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,02</t>
+          <t>9,21; 10,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 15,64</t>
+          <t>14,88; 15,66</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,24; 15,05</t>
+          <t>14,22; 15,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,37; 13,13</t>
+          <t>12,35; 13,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,27</t>
+          <t>11,52; 12,35</t>
         </is>
       </c>
     </row>
